--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>交易编号</t>
   </si>
@@ -52,9 +52,6 @@
   </si>
   <si>
     <t>会计分类</t>
-  </si>
-  <si>
-    <t>交易通道代码</t>
   </si>
   <si>
     <t>成交数量</t>
@@ -83,10 +80,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
   <fonts count="20">
@@ -99,20 +96,58 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -120,48 +155,56 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -173,72 +216,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -257,85 +254,151 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -347,19 +410,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,67 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,6 +439,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -460,26 +466,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -490,21 +476,6 @@
         <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -534,6 +505,21 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -542,16 +528,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -560,133 +557,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1050,7 +1047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.1916666666667" customWidth="1"/>
@@ -1065,17 +1062,16 @@
     <col min="10" max="10" width="10.3" style="2" customWidth="1"/>
     <col min="11" max="11" width="10.875" customWidth="1"/>
     <col min="12" max="12" width="21.4916666666667" customWidth="1"/>
-    <col min="13" max="13" width="13.15" customWidth="1"/>
-    <col min="14" max="14" width="11.175" customWidth="1"/>
-    <col min="15" max="15" width="10.625" customWidth="1"/>
-    <col min="16" max="16" width="13.8166666666667" customWidth="1"/>
-    <col min="17" max="17" width="15.7833333333333" customWidth="1"/>
-    <col min="18" max="18" width="14.3583333333333" customWidth="1"/>
-    <col min="19" max="19" width="13.375" customWidth="1"/>
-    <col min="20" max="20" width="12.3833333333333" customWidth="1"/>
+    <col min="13" max="13" width="11.175" customWidth="1"/>
+    <col min="14" max="14" width="10.625" customWidth="1"/>
+    <col min="15" max="15" width="13.8166666666667" customWidth="1"/>
+    <col min="16" max="16" width="15.7833333333333" customWidth="1"/>
+    <col min="17" max="17" width="14.3583333333333" customWidth="1"/>
+    <col min="18" max="18" width="13.375" customWidth="1"/>
+    <col min="19" max="19" width="12.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:20">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1132,9 +1128,6 @@
       </c>
       <c r="S1" s="3" t="s">
         <v>18</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>交易编号</t>
   </si>
@@ -42,13 +42,13 @@
     <t>交易类型</t>
   </si>
   <si>
-    <t>交易日</t>
-  </si>
-  <si>
-    <t>交割日</t>
-  </si>
-  <si>
-    <t>资金交收日</t>
+    <t>交易日期</t>
+  </si>
+  <si>
+    <t>交割日期</t>
+  </si>
+  <si>
+    <t>资金交收日期</t>
   </si>
   <si>
     <t>会计分类</t>
@@ -57,7 +57,7 @@
     <t>成交数量</t>
   </si>
   <si>
-    <t>全价总额</t>
+    <t>交易金额</t>
   </si>
   <si>
     <t>应收利息总额</t>
@@ -67,9 +67,6 @@
   </si>
   <si>
     <t>结算金额</t>
-  </si>
-  <si>
-    <t>本币交易金额</t>
   </si>
   <si>
     <t>资金账户</t>
@@ -80,11 +77,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -95,6 +92,51 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
@@ -102,6 +144,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -110,13 +175,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -124,16 +183,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -150,27 +202,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -184,49 +215,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,37 +245,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -290,120 +413,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -411,24 +426,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,6 +436,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -483,24 +498,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -520,22 +522,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,10 +542,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -557,133 +554,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1047,7 +1044,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:R1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.1916666666667" customWidth="1"/>
@@ -1060,18 +1057,17 @@
     <col min="8" max="8" width="14.4666666666667" customWidth="1"/>
     <col min="9" max="9" width="9.85833333333333" style="2" customWidth="1"/>
     <col min="10" max="10" width="10.3" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.875" customWidth="1"/>
+    <col min="11" max="11" width="14.8" customWidth="1"/>
     <col min="12" max="12" width="21.4916666666667" customWidth="1"/>
     <col min="13" max="13" width="11.175" customWidth="1"/>
     <col min="14" max="14" width="10.625" customWidth="1"/>
     <col min="15" max="15" width="13.8166666666667" customWidth="1"/>
     <col min="16" max="16" width="15.7833333333333" customWidth="1"/>
     <col min="17" max="17" width="14.3583333333333" customWidth="1"/>
-    <col min="18" max="18" width="13.375" customWidth="1"/>
-    <col min="19" max="19" width="12.3833333333333" customWidth="1"/>
+    <col min="18" max="18" width="12.3833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:18">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1125,9 +1121,6 @@
       </c>
       <c r="R1" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>交易编号</t>
   </si>
@@ -70,6 +70,9 @@
   </si>
   <si>
     <t>资金账户</t>
+  </si>
+  <si>
+    <t>数据来源</t>
   </si>
 </sst>
 </file>
@@ -77,11 +80,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="20">
     <font>
@@ -89,6 +92,87 @@
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -100,6 +184,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -107,18 +200,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -130,109 +231,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -245,61 +248,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -311,25 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -341,91 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -442,8 +445,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -452,16 +455,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -481,6 +475,32 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -492,17 +512,6 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -522,17 +531,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,10 +545,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -554,133 +557,133 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1044,7 +1047,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="18.1916666666667" customWidth="1"/>
@@ -1065,9 +1068,10 @@
     <col min="16" max="16" width="15.7833333333333" customWidth="1"/>
     <col min="17" max="17" width="14.3583333333333" customWidth="1"/>
     <col min="18" max="18" width="12.3833333333333" customWidth="1"/>
+    <col min="19" max="19" width="10.4083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:18">
+    <row r="1" s="1" customFormat="1" spans="1:19">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1121,6 +1125,9 @@
       </c>
       <c r="R1" s="3" t="s">
         <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
+++ b/tams-valuation-parent/tams-valuation/src/main/resources/tpl/trademanage/bond/TrdBondTrade001.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="27">
   <si>
     <t>交易编号</t>
   </si>
@@ -66,7 +66,31 @@
     <t>币种</t>
   </si>
   <si>
-    <t>结算金额</t>
+    <t>经手费</t>
+  </si>
+  <si>
+    <t>结算费</t>
+  </si>
+  <si>
+    <t>净佣金</t>
+  </si>
+  <si>
+    <t>交易手续费</t>
+  </si>
+  <si>
+    <t>结算服务费</t>
+  </si>
+  <si>
+    <t>应付佣金</t>
+  </si>
+  <si>
+    <t>清算金额</t>
+  </si>
+  <si>
+    <t>申购金额</t>
+  </si>
+  <si>
+    <t>中签金额</t>
   </si>
   <si>
     <t>资金账户</t>
@@ -80,13 +104,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="#,##0.00_ "/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,6 +119,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="9.8"/>
+      <color rgb="FF067D17"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
       <name val="宋体"/>
@@ -102,24 +139,102 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -131,111 +246,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -248,25 +278,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -278,157 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -439,24 +469,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -471,6 +483,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -492,10 +519,26 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -516,26 +559,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -545,10 +575,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -557,142 +587,143 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1047,87 +1078,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:AA1"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="18.1916666666667" customWidth="1"/>
-    <col min="2" max="2" width="17.65" customWidth="1"/>
-    <col min="3" max="3" width="18.6416666666667" customWidth="1"/>
-    <col min="4" max="4" width="24.3333333333333" customWidth="1"/>
+    <col min="1" max="1" width="18.0833333333333" customWidth="1"/>
+    <col min="2" max="2" width="17.3166666666667" customWidth="1"/>
+    <col min="3" max="3" width="19.6166666666667" customWidth="1"/>
+    <col min="4" max="4" width="21.9333333333333" customWidth="1"/>
     <col min="5" max="5" width="15.25" customWidth="1"/>
-    <col min="6" max="6" width="19.8333333333333" customWidth="1"/>
-    <col min="7" max="7" width="12.1666666666667" customWidth="1"/>
-    <col min="8" max="8" width="14.4666666666667" customWidth="1"/>
-    <col min="9" max="9" width="9.85833333333333" style="2" customWidth="1"/>
-    <col min="10" max="10" width="10.3" style="2" customWidth="1"/>
-    <col min="11" max="11" width="14.8" customWidth="1"/>
-    <col min="12" max="12" width="21.4916666666667" customWidth="1"/>
-    <col min="13" max="13" width="11.175" customWidth="1"/>
-    <col min="14" max="14" width="10.625" customWidth="1"/>
-    <col min="15" max="15" width="13.8166666666667" customWidth="1"/>
-    <col min="16" max="16" width="15.7833333333333" customWidth="1"/>
-    <col min="17" max="17" width="14.3583333333333" customWidth="1"/>
-    <col min="18" max="18" width="12.3833333333333" customWidth="1"/>
-    <col min="19" max="19" width="10.4083333333333" customWidth="1"/>
+    <col min="6" max="6" width="19.25" customWidth="1"/>
+    <col min="7" max="7" width="14.1416666666667" customWidth="1"/>
+    <col min="8" max="8" width="16.7666666666667" customWidth="1"/>
+    <col min="9" max="9" width="13.2583333333333" style="2" customWidth="1"/>
+    <col min="10" max="10" width="13" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.8416666666667" customWidth="1"/>
+    <col min="12" max="12" width="15.3416666666667" customWidth="1"/>
+    <col min="13" max="14" width="12.3833333333333" customWidth="1"/>
+    <col min="15" max="15" width="14.1333333333333" customWidth="1"/>
+    <col min="16" max="19" width="9.20833333333333" customWidth="1"/>
+    <col min="20" max="20" width="10.9666666666667" customWidth="1"/>
+    <col min="21" max="22" width="10.525" customWidth="1"/>
+    <col min="23" max="25" width="12.3833333333333" customWidth="1"/>
+    <col min="26" max="26" width="12.1666666666667" customWidth="1"/>
+    <col min="27" max="27" width="11.1833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:19">
+    <row r="1" s="1" customFormat="1" spans="1:27">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
